--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.01_b0.01_x0.10_Q80_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.01_b0.01_x0.10_Q80_LO.xlsx
@@ -455,10 +455,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008951669328285136</v>
+        <v>0.007927275227416538</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008951669328285136</v>
+        <v>0.007927275227416538</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.01670473393797371</v>
+        <v>0.01523486616662942</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01670473393797371</v>
+        <v>0.01523486616662942</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -483,10 +483,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03477977638646929</v>
+        <v>0.03161138747782252</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03477977638646929</v>
+        <v>0.03161138747782252</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -497,10 +497,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.05905258952149588</v>
+        <v>0.05380809060320321</v>
       </c>
       <c r="C5" t="n">
-        <v>0.05905258952149588</v>
+        <v>0.05380809060320321</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -511,10 +511,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.07193252123327536</v>
+        <v>0.0655653521201038</v>
       </c>
       <c r="C6" t="n">
-        <v>0.07193252123327536</v>
+        <v>0.0655653521201038</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -525,10 +525,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.07006657476016201</v>
+        <v>0.06373843767934866</v>
       </c>
       <c r="C7" t="n">
-        <v>0.07006657476016201</v>
+        <v>0.06373843767934866</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -539,10 +539,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.06277155324766791</v>
+        <v>0.05714849786760621</v>
       </c>
       <c r="C8" t="n">
-        <v>0.06277155324766791</v>
+        <v>0.05714849786760621</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.05780884778336445</v>
+        <v>0.05270653378206509</v>
       </c>
       <c r="C9" t="n">
-        <v>0.05780884778336445</v>
+        <v>0.05270653378206509</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -567,10 +567,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.05719042200500971</v>
+        <v>0.05221689094398747</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05719042200500971</v>
+        <v>0.05221689094398747</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -581,10 +581,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.05200154595919706</v>
+        <v>0.04748242971383367</v>
       </c>
       <c r="C11" t="n">
-        <v>0.05200154595919706</v>
+        <v>0.04748242971383367</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
